--- a/docs/mtc_infraestructura_vial_panel.xlsx
+++ b/docs/mtc_infraestructura_vial_panel.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/GITHUB/Master Thesis ENA/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianoriega/GITHUB/Master Thesis ENA/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{685F34EA-FC30-9844-BFED-BEBABFC7B4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862A85DC-8C64-444A-AC96-977563D77C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14260" yWindow="600" windowWidth="14160" windowHeight="15780" xr2:uid="{5E679C7F-3B0A-5E4C-98C8-B5F7DDB7235F}"/>
+    <workbookView xWindow="28180" yWindow="980" windowWidth="20960" windowHeight="17160" xr2:uid="{5E679C7F-3B0A-5E4C-98C8-B5F7DDB7235F}"/>
   </bookViews>
   <sheets>
     <sheet name="PCT_PAV_VECINAL TOTAL" sheetId="1" r:id="rId1"/>
     <sheet name="PAV_VECINAL_2017" sheetId="2" r:id="rId2"/>
     <sheet name="PAV_VECINAL_2018" sheetId="3" r:id="rId3"/>
     <sheet name="PAV_VECINAL_2022" sheetId="4" r:id="rId4"/>
+    <sheet name="PAV_VECINAL_2023" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="42">
   <si>
     <t>DEPARTAMENTO</t>
   </si>
@@ -165,6 +166,9 @@
   </si>
   <si>
     <t>% PAVIMENTADO</t>
+  </si>
+  <si>
+    <t>PCT_PAV_VECINAL_2023</t>
   </si>
 </sst>
 </file>
@@ -202,10 +206,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,14 +544,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BBD505-2354-984B-93D6-9C673602B522}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,420 +564,520 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <f>ROUND(PAV_VECINAL_2017!J4, 2)</f>
         <v>0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <f>ROUND(PAV_VECINAL_2018!J4, 2)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <f>ROUND(PAV_VECINAL_2022!J4, 2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J4, 2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <f>ROUND(PAV_VECINAL_2017!J5, 2)</f>
         <v>1.5</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>ROUND(PAV_VECINAL_2018!J5, 2)</f>
         <v>1.47</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <f>ROUND(PAV_VECINAL_2022!J5, 2)</f>
         <v>1.65</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J5, 2)</f>
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <f>ROUND(PAV_VECINAL_2017!J6, 2)</f>
         <v>0.15</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <f>ROUND(PAV_VECINAL_2018!J6, 2)</f>
         <v>0.15</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <f>ROUND(PAV_VECINAL_2022!J6, 2)</f>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J6, 2)</f>
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <f>ROUND(PAV_VECINAL_2017!J7, 2)</f>
         <v>6.51</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <f>ROUND(PAV_VECINAL_2018!J7, 2)</f>
         <v>6.53</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <f>ROUND(PAV_VECINAL_2022!J7, 2)</f>
         <v>8.73</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J7, 2)</f>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <f>ROUND(PAV_VECINAL_2017!J8, 2)</f>
         <v>0.22</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <f>ROUND(PAV_VECINAL_2018!J8, 2)</f>
         <v>0.22</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <f>ROUND(PAV_VECINAL_2022!J8, 2)</f>
         <v>2.39</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J8, 2)</f>
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <f>ROUND(PAV_VECINAL_2017!J9, 2)</f>
         <v>0.34</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <f>ROUND(PAV_VECINAL_2018!J9, 2)</f>
         <v>0.33</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <f>ROUND(PAV_VECINAL_2022!J9, 2)</f>
         <v>0.61</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J9, 2)</f>
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <f>ROUND(PAV_VECINAL_2017!J11, 2)</f>
         <v>1.1599999999999999</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f>ROUND(PAV_VECINAL_2018!J11, 2)</f>
         <v>0.94</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <f>ROUND(PAV_VECINAL_2022!J11, 2)</f>
         <v>2.59</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J11, 2)</f>
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <f>ROUND(PAV_VECINAL_2017!J12, 2)</f>
         <v>0.01</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f>ROUND(PAV_VECINAL_2018!J12, 2)</f>
         <v>0.01</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <f>ROUND(PAV_VECINAL_2022!J12, 2)</f>
         <v>0.01</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J12, 2)</f>
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <f>ROUND(PAV_VECINAL_2017!J13, 2)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <f>ROUND(PAV_VECINAL_2018!J13, 2)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <f>ROUND(PAV_VECINAL_2022!J13, 2)</f>
         <v>2.2200000000000002</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J13, 2)</f>
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <f>ROUND(PAV_VECINAL_2017!J14, 2)</f>
         <v>4.01</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <f>ROUND(PAV_VECINAL_2018!J14, 2)</f>
         <v>3.97</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <f>ROUND(PAV_VECINAL_2022!J14, 2)</f>
         <v>9.27</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J14, 2)</f>
+        <v>9.5299999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <f>ROUND(PAV_VECINAL_2017!J15, 2)</f>
         <v>2.4</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <f>ROUND(PAV_VECINAL_2018!J15, 2)</f>
         <v>2.34</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <f>ROUND(PAV_VECINAL_2022!J15, 2)</f>
         <v>3.72</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J15, 2)</f>
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <f>ROUND(PAV_VECINAL_2017!J16, 2)</f>
         <v>2.8</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <f>ROUND(PAV_VECINAL_2018!J16, 2)</f>
         <v>2.78</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <f>ROUND(PAV_VECINAL_2022!J16, 2)</f>
         <v>2.89</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J16, 2)</f>
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <f>ROUND(PAV_VECINAL_2017!J17, 2)</f>
         <v>1.34</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <f>ROUND(PAV_VECINAL_2018!J17, 2)</f>
         <v>1.34</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <f>ROUND(PAV_VECINAL_2022!J17, 2)</f>
         <v>1.34</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J17, 2)</f>
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <f>ROUND(PAV_VECINAL_2017!J18, 2)</f>
         <v>4.03</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <f>ROUND(PAV_VECINAL_2018!J18, 2)</f>
         <v>3.91</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <f>ROUND(PAV_VECINAL_2022!J18, 2)</f>
         <v>3.71</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J18, 2)</f>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <f>ROUND(PAV_VECINAL_2017!J19, 2)</f>
         <v>4.3499999999999996</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <f>ROUND(PAV_VECINAL_2018!J19, 2)</f>
         <v>4.29</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <f>ROUND(PAV_VECINAL_2022!J19, 2)</f>
         <v>13.34</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J19, 2)</f>
+        <v>13.34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <f>ROUND(PAV_VECINAL_2017!J20, 2)</f>
         <v>0.37</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <f>ROUND(PAV_VECINAL_2018!J20, 2)</f>
         <v>0.49</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <f>ROUND(PAV_VECINAL_2022!J20, 2)</f>
         <v>0.49</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J20, 2)</f>
+        <v>2.5299999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <f>ROUND(PAV_VECINAL_2017!J21, 2)</f>
         <v>7.87</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <f>ROUND(PAV_VECINAL_2018!J21, 2)</f>
         <v>7.89</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <f>ROUND(PAV_VECINAL_2022!J21, 2)</f>
         <v>7.01</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J21, 2)</f>
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <f>ROUND(PAV_VECINAL_2017!J22, 2)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <f>ROUND(PAV_VECINAL_2018!J22, 2)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <f>ROUND(PAV_VECINAL_2022!J22, 2)</f>
         <v>0.63</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J22, 2)</f>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <f>ROUND(PAV_VECINAL_2017!J23, 2)</f>
         <v>2.58</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f>ROUND(PAV_VECINAL_2018!J23, 2)</f>
         <v>2.58</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <f>ROUND(PAV_VECINAL_2022!J23, 2)</f>
         <v>5.08</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J23, 2)</f>
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <f>ROUND(PAV_VECINAL_2017!J24, 2)</f>
         <v>0.49</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <f>ROUND(PAV_VECINAL_2018!J24, 2)</f>
         <v>0.48</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <f>ROUND(PAV_VECINAL_2022!J24, 2)</f>
         <v>0.93</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J24, 2)</f>
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <f>ROUND(PAV_VECINAL_2017!J25, 2)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <f>ROUND(PAV_VECINAL_2018!J25, 2)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <f>ROUND(PAV_VECINAL_2022!J25, 2)</f>
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J25, 2)</f>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <f>ROUND(PAV_VECINAL_2017!J26, 2)</f>
         <v>11.72</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <f>ROUND(PAV_VECINAL_2018!J26, 2)</f>
         <v>11.69</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <f>ROUND(PAV_VECINAL_2022!J26, 2)</f>
         <v>15.21</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J26, 2)</f>
+        <v>15.39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <f>ROUND(PAV_VECINAL_2017!J27, 2)</f>
         <v>1.8</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <f>ROUND(PAV_VECINAL_2018!J27, 2)</f>
         <v>1.64</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <f>ROUND(PAV_VECINAL_2022!J27, 2)</f>
         <v>2.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J27, 2)</f>
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <f>ROUND(PAV_VECINAL_2017!J28, 2)</f>
         <v>0.26</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <f>ROUND(PAV_VECINAL_2018!J28, 2)</f>
         <v>0.26</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <f>ROUND(PAV_VECINAL_2022!J28, 2)</f>
+        <v>0.26</v>
+      </c>
+      <c r="E26" s="1">
+        <f>ROUND(PAV_VECINAL_2023!J28, 2)</f>
         <v>0.26</v>
       </c>
     </row>
@@ -996,44 +1100,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
       <c r="C3" t="s">
         <v>31</v>
       </c>
@@ -1046,9 +1150,9 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
       <c r="J3" t="s">
         <v>40</v>
       </c>
@@ -1444,44 +1548,44 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
       <c r="C3" t="s">
         <v>31</v>
       </c>
@@ -1494,9 +1598,9 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
       <c r="J3" t="s">
         <v>40</v>
       </c>
@@ -1886,44 +1990,44 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
       <c r="C3" t="s">
         <v>31</v>
       </c>
@@ -1936,9 +2040,9 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
       <c r="J3" t="s">
         <v>40</v>
       </c>
@@ -2312,6 +2416,454 @@
       <c r="J28">
         <f t="shared" si="0"/>
         <v>0.25629596612435923</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:G3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B740BF9C-EA46-8445-95FE-8AF790B4FCEE}">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1870.3260000000002</v>
+      </c>
+      <c r="J4">
+        <f>B4/I4*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>178.64499999999998</v>
+      </c>
+      <c r="I5">
+        <v>7626.8080000000009</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J28" si="0">B5/I5*100</f>
+        <v>2.3423298449364394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>125.67</v>
+      </c>
+      <c r="I6">
+        <v>5627.4450000000015</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>2.2331626519672776</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>617.48100000000022</v>
+      </c>
+      <c r="I7">
+        <v>7060.1070000000018</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>8.7460572481408576</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>229.89399999999995</v>
+      </c>
+      <c r="I8">
+        <v>8935.982</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>2.5726775188222173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>244.28300000000002</v>
+      </c>
+      <c r="I9">
+        <v>12973.300000000025</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>1.8829673251986738</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>358.91900000000015</v>
+      </c>
+      <c r="I11">
+        <v>12675.223000000011</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>2.8316582674719006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>22.15</v>
+      </c>
+      <c r="I12">
+        <v>4854.7299999999987</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>0.45625606367398397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>146.95099999999999</v>
+      </c>
+      <c r="I13">
+        <v>5832.0279999999993</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>2.5197238422037755</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>216.15499999999994</v>
+      </c>
+      <c r="I14">
+        <v>2268.58</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>9.5282070722654684</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>339.66999999999996</v>
+      </c>
+      <c r="I15">
+        <v>9159.4750000000058</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>3.7084003177037959</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>285.97000000000003</v>
+      </c>
+      <c r="I16">
+        <v>5652.3290000000015</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>5.0593304105263508</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>36.338999999999999</v>
+      </c>
+      <c r="I17">
+        <v>2063.4209999999998</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>1.7611044958832929</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>160.04899999999998</v>
+      </c>
+      <c r="I18">
+        <v>4323.3199999999988</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>3.7019929128540108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>60.63000000000001</v>
+      </c>
+      <c r="I19">
+        <v>454.33</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>13.344925494684484</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>32.983999999999995</v>
+      </c>
+      <c r="I20">
+        <v>1301.607</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>2.5340982339523368</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>152.96500000000006</v>
+      </c>
+      <c r="I21">
+        <v>1559.251</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>9.8101588519103124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>13.381</v>
+      </c>
+      <c r="I22">
+        <v>2090.8749999999995</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>0.63997130387995471</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>379.81800000000015</v>
+      </c>
+      <c r="I23">
+        <v>6548.4769999999999</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>5.8000967247804365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>142.935</v>
+      </c>
+      <c r="I24">
+        <v>9244.4879999999976</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>1.5461645901860659</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>122.08699999999999</v>
+      </c>
+      <c r="I25">
+        <v>3820.1499999999983</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>3.1958692721490003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>235.99099999999993</v>
+      </c>
+      <c r="I26">
+        <v>1533.4380000000001</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>15.389666879260844</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>60.023000000000003</v>
+      </c>
+      <c r="I27">
+        <v>584.13300000000015</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>10.275570803224605</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>2.3200000000000003</v>
+      </c>
+      <c r="I28">
+        <v>895.20200000000011</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>0.25915938525606513</v>
       </c>
     </row>
   </sheetData>
